--- a/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
+++ b/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anama\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b808ff425a94bbdc/Documents/Faculdade/Iniciação Científica/ARNA_UFPE/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{867AB3C8-3C59-4523-86B1-E5813294B518}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
+    <workbookView xWindow="1100" yWindow="1100" windowWidth="14400" windowHeight="7270" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Atividades" sheetId="1" r:id="rId1"/>
@@ -135,19 +135,19 @@
     <t>absoluto</t>
   </si>
   <si>
-    <t>Custo fixo</t>
-  </si>
-  <si>
-    <t>Custo por unidade de tempo</t>
-  </si>
-  <si>
-    <t>Custo fixo adicional</t>
-  </si>
-  <si>
-    <t>descricao do risco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nome </t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Custo Fixo</t>
+  </si>
+  <si>
+    <t>Custo por Unidade de Tempo</t>
+  </si>
+  <si>
+    <t>Custo Fixo Adicional</t>
   </si>
 </sst>
 </file>
@@ -248,6 +248,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -587,7 +591,7 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
@@ -620,13 +624,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O1" s="6"/>
       <c r="P1" s="3"/>
@@ -1116,7 +1120,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
@@ -1146,10 +1150,10 @@
         <v>16</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>

--- a/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
+++ b/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b808ff425a94bbdc/Documents/Faculdade/Iniciação Científica/ARNA_UFPE/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{867AB3C8-3C59-4523-86B1-E5813294B518}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDBC559A-747A-4CBD-8289-FF64092B487B}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="1100" windowWidth="14400" windowHeight="7270" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Atividades" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
   <si>
     <t>Tipo</t>
   </si>
@@ -248,10 +248,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -963,9 +959,7 @@
       <c r="C10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>

--- a/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
+++ b/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b808ff425a94bbdc/Documents/Faculdade/Iniciação Científica/ARNA_UFPE/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDBC559A-747A-4CBD-8289-FF64092B487B}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48410181-3A5E-4AE8-A8EC-B424626CEB83}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Atividades" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
-  <si>
-    <t>Tipo</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -48,33 +45,15 @@
     <t>Tipo de Distribuicao</t>
   </si>
   <si>
-    <t>Tempo Otimista</t>
-  </si>
-  <si>
-    <t>Tempo Provavel</t>
-  </si>
-  <si>
-    <t>Tempo Pessimista</t>
-  </si>
-  <si>
     <t>Tempo Minimo</t>
   </si>
   <si>
-    <t>Tempo Moda</t>
-  </si>
-  <si>
     <t>Tempo Maximo</t>
   </si>
   <si>
     <t>Tempo Medio</t>
   </si>
   <si>
-    <t>Custo</t>
-  </si>
-  <si>
-    <t>Probabilidade</t>
-  </si>
-  <si>
     <t>Atividades Afetadas</t>
   </si>
   <si>
@@ -87,18 +66,12 @@
     <t>Atraso Maximo</t>
   </si>
   <si>
-    <t>Descricao</t>
-  </si>
-  <si>
     <t>Atividade</t>
   </si>
   <si>
     <t>beta_pert</t>
   </si>
   <si>
-    <t>descricao da atividade</t>
-  </si>
-  <si>
     <t>triangular</t>
   </si>
   <si>
@@ -148,6 +121,24 @@
   </si>
   <si>
     <t>Custo Fixo Adicional</t>
+  </si>
+  <si>
+    <t>Tipo de Risco</t>
+  </si>
+  <si>
+    <t>Probabilidade do Risco Ocorrer</t>
+  </si>
+  <si>
+    <t>Custo Variavel Adicional</t>
+  </si>
+  <si>
+    <t>Desvio Padrao</t>
+  </si>
+  <si>
+    <t>Probabilidade do Tempo Otimista</t>
+  </si>
+  <si>
+    <t>Probabilidade do Atraso Otimista</t>
   </si>
 </sst>
 </file>
@@ -248,6 +239,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -577,8 +572,9 @@
     <col min="5" max="5" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.7265625" customWidth="1"/>
     <col min="7" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="29.26953125" customWidth="1"/>
     <col min="10" max="10" width="10.54296875" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
     <col min="14" max="14" width="22.453125" customWidth="1"/>
     <col min="15" max="15" width="16.26953125" customWidth="1"/>
     <col min="16" max="16" width="12.81640625" bestFit="1" customWidth="1"/>
@@ -587,46 +583,37 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="O1" s="6"/>
       <c r="P1" s="3"/>
@@ -635,14 +622,14 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E2" s="6">
         <v>3</v>
@@ -653,17 +640,10 @@
       <c r="G2" s="6">
         <v>8</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6">
+      <c r="J2" s="6">
         <v>100</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="6">
+      <c r="K2" s="6">
         <v>1.3</v>
       </c>
       <c r="O2" s="6"/>
@@ -673,7 +653,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B3" s="6">
         <v>2</v>
@@ -682,28 +662,21 @@
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6">
+        <v>12</v>
+      </c>
+      <c r="E3" s="6">
         <v>3</v>
       </c>
-      <c r="I3" s="6">
+      <c r="F3" s="6">
         <v>6</v>
       </c>
+      <c r="G3" s="6">
+        <v>10</v>
+      </c>
       <c r="J3" s="6">
-        <v>10</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6">
         <v>0</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" s="6">
+      <c r="K3" s="6">
         <v>0.2</v>
       </c>
       <c r="O3" s="6"/>
@@ -713,35 +686,28 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B4" s="6">
         <v>3</v>
       </c>
       <c r="C4" s="6">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="6"/>
       <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6">
-        <v>1</v>
-      </c>
-      <c r="I4" s="6"/>
+      <c r="G4" s="6">
+        <v>4</v>
+      </c>
       <c r="J4" s="6">
-        <v>4</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6">
         <v>0</v>
       </c>
-      <c r="M4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="6">
+      <c r="K4" s="6">
         <v>0.2</v>
       </c>
       <c r="O4" s="6"/>
@@ -751,7 +717,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B5" s="6">
         <v>4</v>
@@ -760,28 +726,20 @@
         <v>2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="6">
-        <v>4</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6">
-        <v>8</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6">
+        <v>6</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5">
+        <v>0.2</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
       <c r="K5" s="6">
-        <v>6</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="6">
         <v>0.2</v>
       </c>
       <c r="O5" s="6"/>
@@ -791,16 +749,14 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="6">
-        <v>2</v>
-      </c>
+      <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E6" s="6">
         <v>8</v>
@@ -811,17 +767,10 @@
       <c r="G6" s="6">
         <v>12</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6">
+      <c r="J6" s="6">
         <v>0</v>
       </c>
-      <c r="M6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" s="6">
+      <c r="K6" s="6">
         <v>0.2</v>
       </c>
       <c r="O6" s="6"/>
@@ -831,7 +780,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B7" s="6">
         <v>6</v>
@@ -840,7 +789,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E7" s="6">
         <v>3</v>
@@ -851,17 +800,10 @@
       <c r="G7" s="6">
         <v>6</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6">
+      <c r="J7" s="6">
         <v>0</v>
       </c>
-      <c r="M7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="6">
+      <c r="K7" s="6">
         <v>0.2</v>
       </c>
       <c r="O7" s="6"/>
@@ -871,16 +813,16 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="6">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E8" s="6">
         <v>7</v>
@@ -891,17 +833,10 @@
       <c r="G8" s="6">
         <v>11</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6">
+      <c r="J8" s="6">
         <v>0</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N8" s="6">
+      <c r="K8" s="6">
         <v>0.2</v>
       </c>
       <c r="O8" s="6"/>
@@ -911,7 +846,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B9" s="6">
         <v>8</v>
@@ -920,7 +855,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E9" s="6">
         <v>3</v>
@@ -931,17 +866,10 @@
       <c r="G9" s="6">
         <v>6</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6">
+      <c r="J9" s="6">
         <v>0</v>
       </c>
-      <c r="M9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N9" s="6">
+      <c r="K9" s="6">
         <v>0.2</v>
       </c>
       <c r="O9" s="6"/>
@@ -951,30 +879,23 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6">
+      <c r="J10" s="6">
         <v>0</v>
       </c>
-      <c r="M10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="6">
-        <v>0.2</v>
+      <c r="K10" s="6">
+        <v>0</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="3"/>
@@ -989,11 +910,8 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
@@ -1013,9 +931,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
@@ -1035,9 +951,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
@@ -1057,9 +971,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
@@ -1079,9 +991,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
@@ -1108,152 +1018,156 @@
     <col min="1" max="1" width="10.1796875" customWidth="1"/>
     <col min="2" max="2" width="10.26953125" customWidth="1"/>
     <col min="3" max="3" width="18.1796875" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" customWidth="1"/>
-    <col min="11" max="11" width="20.7265625" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="26.08984375" customWidth="1"/>
+    <col min="8" max="8" width="17.81640625" customWidth="1"/>
+    <col min="9" max="9" width="13.36328125" customWidth="1"/>
+    <col min="10" max="10" width="14.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2" s="6">
         <v>0.5</v>
       </c>
-      <c r="G2" s="6">
+      <c r="H2" s="6">
         <v>1</v>
       </c>
-      <c r="H2" s="6">
+      <c r="I2" s="6">
         <v>3</v>
       </c>
-      <c r="I2" s="6">
+      <c r="J2" s="6">
         <v>4</v>
       </c>
-      <c r="J2" s="6">
+      <c r="K2" s="6">
         <v>5</v>
-      </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6">
-        <v>2</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="7"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6">
         <v>0.3</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="H3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="6">
         <v>0.3</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6">
+      <c r="J3" s="6"/>
+      <c r="K3" s="6">
         <v>0.5</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6">
-        <v>2</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="L4" s="5"/>
+      <c r="F4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="L5" s="5"/>
+      <c r="F5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="L6" s="5"/>
+      <c r="F6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="L7" s="5"/>
+      <c r="F7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="L8" s="5"/>
+      <c r="F8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="L9" s="5"/>
+      <c r="F9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="L10" s="5"/>
+      <c r="F10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
@@ -1267,28 +1181,28 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C13" s="2"/>
-      <c r="L13" s="4"/>
+      <c r="F13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="L14" s="4"/>
+      <c r="F14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C15" s="3"/>
-      <c r="L15" s="4"/>
+      <c r="F15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="L16" s="4"/>
+      <c r="F16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="L17" s="4"/>
+      <c r="F17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
     </row>
@@ -1316,7 +1230,6 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
@@ -1335,7 +1248,6 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
@@ -1343,7 +1255,7 @@
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="L23" s="4"/>
+      <c r="F23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
     </row>

--- a/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
+++ b/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b808ff425a94bbdc/Documents/Faculdade/Iniciação Científica/ARNA_UFPE/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48410181-3A5E-4AE8-A8EC-B424626CEB83}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3709F80B-87F9-49D4-A54C-B02412F5A84C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Tempo Maximo</t>
   </si>
   <si>
-    <t>Tempo Medio</t>
-  </si>
-  <si>
     <t>Atividades Afetadas</t>
   </si>
   <si>
@@ -139,6 +136,15 @@
   </si>
   <si>
     <t>Probabilidade do Atraso Otimista</t>
+  </si>
+  <si>
+    <t>Tempo Mais Provavel</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Tipo de Distribuicao da Consequencia</t>
   </si>
 </sst>
 </file>
@@ -570,11 +576,12 @@
     <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.26953125" customWidth="1"/>
     <col min="5" max="5" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7265625" customWidth="1"/>
-    <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="29.26953125" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="29.26953125" customWidth="1"/>
+    <col min="11" max="11" width="10.54296875" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="22.453125" customWidth="1"/>
     <col min="15" max="15" width="16.26953125" customWidth="1"/>
     <col min="16" max="16" width="12.81640625" bestFit="1" customWidth="1"/>
@@ -583,7 +590,7 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -598,22 +605,25 @@
         <v>3</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="O1" s="6"/>
       <c r="P1" s="3"/>
@@ -622,14 +632,14 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="6">
         <v>3</v>
@@ -640,10 +650,10 @@
       <c r="G2" s="6">
         <v>8</v>
       </c>
-      <c r="J2" s="6">
+      <c r="K2" s="6">
         <v>100</v>
       </c>
-      <c r="K2" s="6">
+      <c r="L2" s="6">
         <v>1.3</v>
       </c>
       <c r="O2" s="6"/>
@@ -653,7 +663,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="6">
         <v>2</v>
@@ -662,7 +672,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="6">
         <v>3</v>
@@ -673,10 +683,10 @@
       <c r="G3" s="6">
         <v>10</v>
       </c>
-      <c r="J3" s="6">
+      <c r="K3" s="6">
         <v>0</v>
       </c>
-      <c r="K3" s="6">
+      <c r="L3" s="6">
         <v>0.2</v>
       </c>
       <c r="O3" s="6"/>
@@ -686,7 +696,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="6">
         <v>3</v>
@@ -695,7 +705,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -704,10 +714,10 @@
       <c r="G4" s="6">
         <v>4</v>
       </c>
-      <c r="J4" s="6">
+      <c r="K4" s="6">
         <v>0</v>
       </c>
-      <c r="K4" s="6">
+      <c r="L4" s="6">
         <v>0.2</v>
       </c>
       <c r="O4" s="6"/>
@@ -717,7 +727,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="6">
         <v>4</v>
@@ -726,20 +736,21 @@
         <v>2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="6">
-        <v>6</v>
-      </c>
+      <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
         <v>0.2</v>
       </c>
-      <c r="J5" s="6">
+      <c r="K5" s="6">
         <v>0</v>
       </c>
-      <c r="K5" s="6">
+      <c r="L5" s="6">
         <v>0.2</v>
       </c>
       <c r="O5" s="6"/>
@@ -749,14 +760,14 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="6">
         <v>5</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="6">
         <v>8</v>
@@ -767,10 +778,10 @@
       <c r="G6" s="6">
         <v>12</v>
       </c>
-      <c r="J6" s="6">
+      <c r="K6" s="6">
         <v>0</v>
       </c>
-      <c r="K6" s="6">
+      <c r="L6" s="6">
         <v>0.2</v>
       </c>
       <c r="O6" s="6"/>
@@ -780,7 +791,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="6">
         <v>6</v>
@@ -789,7 +800,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="6">
         <v>3</v>
@@ -800,10 +811,10 @@
       <c r="G7" s="6">
         <v>6</v>
       </c>
-      <c r="J7" s="6">
+      <c r="K7" s="6">
         <v>0</v>
       </c>
-      <c r="K7" s="6">
+      <c r="L7" s="6">
         <v>0.2</v>
       </c>
       <c r="O7" s="6"/>
@@ -813,16 +824,16 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="6">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="6">
         <v>7</v>
@@ -833,10 +844,10 @@
       <c r="G8" s="6">
         <v>11</v>
       </c>
-      <c r="J8" s="6">
+      <c r="K8" s="6">
         <v>0</v>
       </c>
-      <c r="K8" s="6">
+      <c r="L8" s="6">
         <v>0.2</v>
       </c>
       <c r="O8" s="6"/>
@@ -846,7 +857,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="6">
         <v>8</v>
@@ -855,7 +866,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6">
         <v>3</v>
@@ -866,10 +877,10 @@
       <c r="G9" s="6">
         <v>6</v>
       </c>
-      <c r="J9" s="6">
+      <c r="K9" s="6">
         <v>0</v>
       </c>
-      <c r="K9" s="6">
+      <c r="L9" s="6">
         <v>0.2</v>
       </c>
       <c r="O9" s="6"/>
@@ -879,22 +890,22 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
-      <c r="J10" s="6">
+      <c r="K10" s="6">
         <v>0</v>
       </c>
-      <c r="K10" s="6">
+      <c r="L10" s="6">
         <v>0</v>
       </c>
       <c r="O10" s="6"/>
@@ -910,9 +921,8 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="J11" s="6"/>
       <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
+      <c r="L11" s="6"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="3"/>
@@ -930,9 +940,8 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="K12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
@@ -950,9 +959,8 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="K13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
@@ -970,9 +978,8 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="L14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="K14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
@@ -990,9 +997,8 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="L15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="K15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -1018,10 +1024,10 @@
     <col min="1" max="1" width="10.1796875" customWidth="1"/>
     <col min="2" max="2" width="10.26953125" customWidth="1"/>
     <col min="3" max="3" width="18.1796875" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="4" max="4" width="26.54296875" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="17.453125" customWidth="1"/>
-    <col min="7" max="7" width="26.08984375" customWidth="1"/>
+    <col min="7" max="7" width="31.90625" customWidth="1"/>
     <col min="8" max="8" width="17.81640625" customWidth="1"/>
     <col min="9" max="9" width="13.36328125" customWidth="1"/>
     <col min="10" max="10" width="14.1796875" customWidth="1"/>
@@ -1030,63 +1036,63 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>9</v>
-      </c>
       <c r="L1" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="C2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>12</v>
+        <v>22</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.5</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6">
         <v>2</v>
       </c>
-      <c r="G2" s="6">
-        <v>0.5</v>
+      <c r="G2" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="H2" s="6">
         <v>1</v>
@@ -1105,26 +1111,26 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.3</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6">
         <v>2</v>
       </c>
-      <c r="G3" s="6">
-        <v>0.3</v>
+      <c r="G3" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="6">
         <v>0.3</v>

--- a/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
+++ b/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b808ff425a94bbdc/Documents/Faculdade/Iniciação Científica/ARNA_UFPE/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3709F80B-87F9-49D4-A54C-B02412F5A84C}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79FBEE44-0125-4E89-95DD-5734F2E43875}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Atividades" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -57,9 +57,6 @@
     <t>Atraso Minimo</t>
   </si>
   <si>
-    <t>Atraso Medio</t>
-  </si>
-  <si>
     <t>Atraso Maximo</t>
   </si>
   <si>
@@ -132,12 +129,6 @@
     <t>Desvio Padrao</t>
   </si>
   <si>
-    <t>Probabilidade do Tempo Otimista</t>
-  </si>
-  <si>
-    <t>Probabilidade do Atraso Otimista</t>
-  </si>
-  <si>
     <t>Tempo Mais Provavel</t>
   </si>
   <si>
@@ -145,6 +136,15 @@
   </si>
   <si>
     <t>Tipo de Distribuicao da Consequencia</t>
+  </si>
+  <si>
+    <t>Atraso Mais Provavel</t>
+  </si>
+  <si>
+    <t>Probabilidade do Tempo Minimo</t>
+  </si>
+  <si>
+    <t>Probabilidade do Atraso Minimo</t>
   </si>
 </sst>
 </file>
@@ -590,7 +590,7 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -605,25 +605,25 @@
         <v>3</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="K1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="O1" s="6"/>
       <c r="P1" s="3"/>
@@ -632,14 +632,14 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="6">
         <v>3</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6">
         <v>2</v>
@@ -672,7 +672,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="6">
         <v>3</v>
@@ -696,7 +696,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="6">
         <v>3</v>
@@ -705,7 +705,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -727,7 +727,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6">
         <v>4</v>
@@ -736,7 +736,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -760,14 +760,14 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="6">
         <v>5</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="6">
         <v>8</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="6">
         <v>6</v>
@@ -800,7 +800,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="6">
         <v>3</v>
@@ -824,16 +824,16 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="6">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="6">
         <v>7</v>
@@ -857,7 +857,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="6">
         <v>8</v>
@@ -866,7 +866,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="6">
         <v>3</v>
@@ -890,13 +890,13 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -1030,31 +1030,32 @@
     <col min="7" max="7" width="31.90625" customWidth="1"/>
     <col min="8" max="8" width="17.81640625" customWidth="1"/>
     <col min="9" max="9" width="13.36328125" customWidth="1"/>
-    <col min="10" max="10" width="14.1796875" customWidth="1"/>
+    <col min="10" max="10" width="18.453125" customWidth="1"/>
     <col min="11" max="11" width="13.1796875" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>5</v>
@@ -1063,26 +1064,30 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="L1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="C2" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="6">
         <v>0.5</v>
@@ -1092,7 +1097,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" s="6">
         <v>1</v>
@@ -1111,13 +1116,13 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" s="6">
         <v>0.3</v>
@@ -1127,10 +1132,10 @@
         <v>2</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="6">
         <v>0.3</v>

--- a/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
+++ b/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b808ff425a94bbdc/Documents/Faculdade/Iniciação Científica/ARNA_UFPE/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79FBEE44-0125-4E89-95DD-5734F2E43875}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{770EDF44-B255-479F-AC3D-5F1F12AEC8E3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
   <si>
     <t>ID</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>Probabilidade do Atraso Minimo</t>
+  </si>
+  <si>
+    <t>inicio</t>
   </si>
 </sst>
 </file>
@@ -631,30 +634,11 @@
       <c r="U1" s="4"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="6">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="6">
-        <v>3</v>
-      </c>
-      <c r="F2" s="6">
-        <v>5</v>
-      </c>
-      <c r="G2" s="6">
-        <v>8</v>
-      </c>
-      <c r="K2" s="6">
-        <v>100</v>
-      </c>
-      <c r="L2" s="6">
-        <v>1.3</v>
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="3"/>
@@ -666,28 +650,28 @@
         <v>8</v>
       </c>
       <c r="B3" s="6">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6">
         <v>1</v>
       </c>
+      <c r="C3" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="D3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="6">
         <v>3</v>
       </c>
       <c r="F3" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" s="6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L3" s="6">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="3"/>
@@ -699,20 +683,22 @@
         <v>8</v>
       </c>
       <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="6">
-        <v>2</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="6">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="6">
+        <v>6</v>
+      </c>
       <c r="G4" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K4" s="6">
         <v>0</v>
@@ -730,22 +716,20 @@
         <v>8</v>
       </c>
       <c r="B5" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="6">
         <v>2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
       <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>0.2</v>
+      <c r="G5" s="6">
+        <v>4</v>
       </c>
       <c r="K5" s="6">
         <v>0</v>
@@ -763,20 +747,22 @@
         <v>8</v>
       </c>
       <c r="B6" s="6">
-        <v>5</v>
-      </c>
-      <c r="C6" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2</v>
+      </c>
       <c r="D6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="6">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6">
-        <v>10</v>
-      </c>
-      <c r="G6" s="6">
         <v>12</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>0.2</v>
       </c>
       <c r="K6" s="6">
         <v>0</v>
@@ -794,22 +780,22 @@
         <v>8</v>
       </c>
       <c r="B7" s="6">
-        <v>6</v>
-      </c>
-      <c r="C7" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F7" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K7" s="6">
         <v>0</v>
@@ -827,22 +813,22 @@
         <v>8</v>
       </c>
       <c r="B8" s="6">
-        <v>7</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="C8" s="6">
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G8" s="6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K8" s="6">
         <v>0</v>
@@ -860,22 +846,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>8</v>
-      </c>
-      <c r="C9" s="6">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F9" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G9" s="6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K9" s="6">
         <v>0</v>
@@ -892,21 +878,29 @@
       <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="B10" s="6">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="6">
+        <v>3</v>
+      </c>
+      <c r="F10" s="6">
+        <v>5</v>
+      </c>
+      <c r="G10" s="6">
+        <v>6</v>
+      </c>
       <c r="K10" s="6">
         <v>0</v>
       </c>
       <c r="L10" s="6">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="3"/>
@@ -914,15 +908,25 @@
       <c r="U10" s="4"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="3"/>

--- a/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
+++ b/resources/Modelo - Atividade e Riscos (Monte Carlo).xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b808ff425a94bbdc/Documents/Faculdade/Iniciação Científica/ARNA_UFPE/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anaal\Desktop\Repositorio_ARNA\ARNA_UFPE\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{DA02E661-AE3D-4C1E-B96A-B0C0DA20CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{770EDF44-B255-479F-AC3D-5F1F12AEC8E3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64415AC7-03D9-4A75-9F84-96F14BDA4D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7EB555F7-2C2B-4388-8B33-737FD34076B1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Atividades" sheetId="1" r:id="rId1"/>
-    <sheet name="Riscos" sheetId="2" r:id="rId2"/>
+    <sheet name="Orientações" sheetId="3" r:id="rId1"/>
+    <sheet name="Atividades" sheetId="1" r:id="rId2"/>
+    <sheet name="Riscos" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="77">
   <si>
     <t>ID</t>
   </si>
@@ -148,13 +149,169 @@
   </si>
   <si>
     <t>inicio</t>
+  </si>
+  <si>
+    <t>ORIENTAÇÕES PARA PREENCHIMENTO DA PLANILHA PARA SIMULAÇÃO DE MONTE CARLO</t>
+  </si>
+  <si>
+    <t>(A configuração das colunas não pode ser alterada)</t>
+  </si>
+  <si>
+    <t>A planilha padrão é composta por duas abas: Atividades e Riscos. A aba Atividades é para inclusão dos dados das atividades do projeto.</t>
+  </si>
+  <si>
+    <t>Para aba Atividades:</t>
+  </si>
+  <si>
+    <t>Coluna A (nome): refere-se à identificação das atividades.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coluna B (ID): refere-se à identificação da atividade em forma de números. Por exemplo, caso haja 3 atividades no seu projeto, as atividades na coluna B deverão ser identificadas como 1, 2 e 3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coluna C (precedentes): refere-se a precedência de cada atividade. Caso haja precedência, inserir o a ID (numérica) da atividade precedente. Caso haja mais de uma, inserir separadas por vírgula e espaço. Por exemplo “2, 3” – significa que há exigência da precedência da atividade 2 e 3. </t>
+  </si>
+  <si>
+    <t>Coluna D (Tipo de Distribuição): refere-se ao tipo de distribuição da atividade.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atualmente, é possível utilizar beta_pert, triangular, uniforme, normal, Bernoulli. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a) Para beta_pert e triangular: </t>
+  </si>
+  <si>
+    <t>i.	Inserir dados da distribuição nas colunas E (tempo mínimo), F (tempo médio/mais provável) e G (tempo máximo).</t>
+  </si>
+  <si>
+    <t>b) Para uniforme:</t>
+  </si>
+  <si>
+    <t>i.	Inserir dados da distribuição nas colunas E (tempo mínimo) e G (tempo máximo).</t>
+  </si>
+  <si>
+    <t>c) Para normal:</t>
+  </si>
+  <si>
+    <t>i.	Inserir dados da distribuição nas colunas H (média) e I (desvio padrão)</t>
+  </si>
+  <si>
+    <t>d) Para Bernoulli:</t>
+  </si>
+  <si>
+    <t>i. Inserir dados da distribuição na coluna E (tempo mínimo), na coluna G (tempo máximo) e na coluna J (Probabilidade do Tempo Minimo)</t>
+  </si>
+  <si>
+    <t>Coluna K (custo fixo): refere-se ao custo fixo de cada atividade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coluna L (custo por unidade de tempo): refere-se ao custo variável por unidade de tempo. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observações: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">As atividades são identificadas em forma numérica e os riscos por letras alfabéticas. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>O ARNA EXIGE A INSERÇÃ DA ATIVIDADE fim COMO MARCO FINAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>, identificando quais atividades precedem diretamente o nó final. Ou seja, para a linha direcionada para essa atividade fim, a coluna A deve conter “Atividade”, a coluna B deve conter “fim” e a coluna C deve conter as atividades que estão diretamente ligadas ao fim (por exemplo: atividade 5 e 6 são predecessoras do fim, logo a coluna C deve estar preenchida com “5, 6”).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Caso haja mais de uma informação deve-se inserir separadas por vírgula e espaço. Por exemplo “2, 3” </t>
+  </si>
+  <si>
+    <t>Para acrescentar novas linhas de atividades, utilizar Ctrl + "+"</t>
+  </si>
+  <si>
+    <t>--------------------------------------------------------------------</t>
+  </si>
+  <si>
+    <t>Para aba Riscos (caso não haja riscos, deixar dados em branco ou excluir essa aba)</t>
+  </si>
+  <si>
+    <t>Coluna A (nome): refere-se à identificação dos riscos</t>
+  </si>
+  <si>
+    <t>Coluna B (ID): refere-se à identificação do risco em ordem alfabética (ou seja, ID do primeiro risco será “A” (sem aspas), ID para segundo risco “B” (sem aspas))</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Coluna C (tipo de risco): refere-se a possibilidade do risco atuar de forma absoluta (sendo acrescido como uma soma à duração da(s) atividade(s) afetada(s)) ou do risco atuar de forma percentual (sendo acrescido percentualmente - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>nesse caso, atraso deve ser inserido de forma decimal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>!! por exemplo: 0,3)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Coluna D (probabilidade do risco ocorrer): refere-se à probabilidade do risco acontecer, sendo um dado decimal, entre 0 e 1 (por exemplo, o risco ocorrerá com probabilidade 0,5 (não pode ser inserido 50%). </t>
+  </si>
+  <si>
+    <t>Coluna E (custo variável adicional): refere-se ao custo variável por unidade de tempo do risco.</t>
+  </si>
+  <si>
+    <t>Coluna F (custo fixo adicional): refere-se ao custo fixo do risco.</t>
+  </si>
+  <si>
+    <t>Coluna G (tipo de distribuição da consequência): a consequência para o risco pode ser dada por diferentes tipos de distribuição</t>
+  </si>
+  <si>
+    <t>i.	Inserir dados da distribuição nas colunas I (atraso mínimo), J (atraso médio/mais provável) e K (atraso máximo).</t>
+  </si>
+  <si>
+    <t>i.	Inserir dados da distribuição nas colunas I (atraso mínimo) e K (atraso máximo).</t>
+  </si>
+  <si>
+    <t>i.	Inserir dados da distribuição nas colunas L (média) e M (desvio padrão)</t>
+  </si>
+  <si>
+    <t>i. Inserir dados da distribuição na coluna  I (atraso mínimo) e K (atraso máximo) e e na coluna N (Probabilidade do atraso mínimo)</t>
+  </si>
+  <si>
+    <t>Coluna H (atividades afetadas): refere-se as atividades que serão afetadas pelo risco. Caso o risco afete mais de uma atividade, inseri-las separadas por vírgula e espaço (por exemplo: “2, 3” (sem aspas)).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -203,6 +360,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -224,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
@@ -233,6 +411,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -250,12 +437,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -570,28 +753,273 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7C76CD6-C2B3-4631-9F81-7E62B8E9BC22}">
+  <dimension ref="A1:D50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D12" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D14" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D16" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D40" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C41" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D42" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C43" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D44" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C45" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D46" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB68868-0FDC-4582-AC8B-DC548EFBEDED}">
   <dimension ref="A1:U15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.26953125" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="29.26953125" customWidth="1"/>
-    <col min="11" max="11" width="10.54296875" customWidth="1"/>
+    <col min="10" max="10" width="29.28515625" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="22.453125" customWidth="1"/>
-    <col min="15" max="15" width="16.26953125" customWidth="1"/>
-    <col min="16" max="16" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.42578125" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>23</v>
       </c>
@@ -633,7 +1061,7 @@
       <c r="Q1" s="3"/>
       <c r="U1" s="4"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -645,7 +1073,7 @@
       <c r="Q2" s="3"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
@@ -678,7 +1106,7 @@
       <c r="Q3" s="3"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -711,7 +1139,7 @@
       <c r="Q4" s="3"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
@@ -742,7 +1170,7 @@
       <c r="Q5" s="3"/>
       <c r="U5" s="4"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
@@ -775,7 +1203,7 @@
       <c r="Q6" s="3"/>
       <c r="U6" s="4"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
@@ -808,7 +1236,7 @@
       <c r="Q7" s="3"/>
       <c r="U7" s="4"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
@@ -841,7 +1269,7 @@
       <c r="Q8" s="3"/>
       <c r="U8" s="4"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -874,7 +1302,7 @@
       <c r="Q9" s="3"/>
       <c r="U9" s="4"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
@@ -907,7 +1335,7 @@
       <c r="Q10" s="3"/>
       <c r="U10" s="4"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
@@ -936,7 +1364,7 @@
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -955,7 +1383,7 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -974,7 +1402,7 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -993,7 +1421,7 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1020,26 +1448,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323E7EE9-8952-48A6-8AFB-00EF986B03FF}">
   <dimension ref="A1:Q23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" customWidth="1"/>
-    <col min="4" max="4" width="26.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="17.453125" customWidth="1"/>
-    <col min="7" max="7" width="31.90625" customWidth="1"/>
-    <col min="8" max="8" width="17.81640625" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" customWidth="1"/>
-    <col min="10" max="10" width="18.453125" customWidth="1"/>
-    <col min="11" max="11" width="13.1796875" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="31.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>22</v>
       </c>
@@ -1083,7 +1511,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
@@ -1118,7 +1546,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="7"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -1151,89 +1579,89 @@
       <c r="M3" s="6"/>
       <c r="N3" s="7"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C13" s="2"/>
       <c r="F13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C15" s="3"/>
       <c r="F15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N18" s="4"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N19" s="4"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1251,7 +1679,7 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1269,7 +1697,7 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
